--- a/produkte/Automaten-Rentabilitaetsrechner.xlsx
+++ b/produkte/Automaten-Rentabilitaetsrechner.xlsx
@@ -1950,11 +1950,11 @@
         </is>
       </c>
       <c r="C20" s="35" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="D20" s="28" t="inlineStr">
         <is>
-          <t>Übliche Spanne 0 bis 80 €. Viele Standorte geben die Fläche umsonst her, wenn der Automat gewünscht ist.</t>
+          <t>Übliche Spanne 50 bis 150 €. Frag trotzdem, ob der Betrieb darauf verzichtet — manche geben die Fläche umsonst her, wenn der Automat gewünscht ist.</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="D54" s="28" t="inlineStr">
         <is>
-          <t>Gebraucht 800–2.500 €, neu 3.000–8.000 €. Bei Miete oder Leasing hier 0 eintragen und die Rate unter „Sonstiges“ erfassen.</t>
+          <t>Gebraucht 2.000–4.000 €, neu 5.000–15.000 €. Bei Miete oder Leasing hier 0 eintragen und die Rate unter „Sonstiges“ erfassen.</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C8" s="51" t="inlineStr">
         <is>
-          <t>0 – 80 € / Monat</t>
+          <t>50 – 150 € / Monat</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>Viele Betriebe verlangen nichts, wenn die Belegschaft den Automaten will. Immer zuerst nach der kostenlosen Variante fragen.</t>
+          <t>Frag trotzdem zuerst, ob der Betrieb auf die Miete verzichtet — manche tun das, wenn die Belegschaft den Automaten selbst will.</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C12" s="51" t="inlineStr">
         <is>
-          <t>800 – 2.500 €</t>
+          <t>2.000 – 4.000 €, im Einzelfall mehr</t>
         </is>
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>Auf Ersatzteilversorgung und Münzprüfer achten. Ein Gerät ohne Ersatzteile ist beim ersten Defekt Schrott.</t>
+          <t>Junge Geräte mit Kühlung und Kartenzahlung liegen deutlich darüber. Auf Ersatzteilversorgung und Münzprüfer achten: ein Gerät ohne Ersatzteile ist beim ersten Defekt Schrott.</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="C13" s="51" t="inlineStr">
         <is>
-          <t>3.000 – 8.000 €</t>
+          <t>5.000 – 15.000 €</t>
         </is>
       </c>
       <c r="D13" s="51" t="inlineStr">
         <is>
-          <t>Rechnet sich meist erst ab mehreren Standorten oder bei Kartenzahlung.</t>
+          <t>Die Spanne ist groß: ein einfacher Spiralautomat liegt unten, ein Kombigerät mit Kühlung und Kartenzahlung oben.</t>
         </is>
       </c>
     </row>
